--- a/sheets/민요/검수/아리랑.xlsx
+++ b/sheets/민요/검수/아리랑.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/아리랑.xlsx
+++ b/sheets/민요/검수/아리랑.xlsx
@@ -2503,13 +2503,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
   </cols>
   <sheetData>
